--- a/output/pdf_financials_xlsx/HLS.xlsx
+++ b/output/pdf_financials_xlsx/HLS.xlsx
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.872</v>
+        <v>1.071</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>1.617</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.919</v>
+        <v>1.674</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.838</v>
+        <v>2.109</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.136</v>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>OtherCurrentAssets</t>
+          <t>CurrentAssets</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">

--- a/output/pdf_financials_xlsx/HLS.xlsx
+++ b/output/pdf_financials_xlsx/HLS.xlsx
@@ -1872,19 +1872,19 @@
         <v>47.078</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>21.179</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>20.723</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>21.952</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>17.456</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>11.723</v>
       </c>
     </row>
     <row r="35">
@@ -1950,19 +1950,19 @@
         <v>47.078</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>21.179</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>20.723</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>21.952</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>17.456</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>11.723</v>
       </c>
     </row>
     <row r="37">
@@ -5383,22 +5383,22 @@
         <v>0</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>0</v>
+        <v>-0.453</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.608</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="125">
@@ -5422,22 +5422,22 @@
         <v>0</v>
       </c>
       <c r="F125" s="3" t="n">
-        <v>0</v>
+        <v>-0.453</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>-0.637</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.608</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.53</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="126">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -13014,7 +13014,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E113" t="inlineStr">
         <is>
           <t>-</t>
@@ -14492,7 +14496,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr"/>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E136" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HLS.xlsx
+++ b/output/pdf_financials_xlsx/HLS.xlsx
@@ -14104,7 +14104,11 @@
           <t>Other additions to intangible assets 7</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr"/>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E130" t="inlineStr">
         <is>
           <t>-</t>
@@ -15690,7 +15694,11 @@
           <t>Other additions to intangible assets</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E155" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/HLS.xlsx
+++ b/output/pdf_financials_xlsx/HLS.xlsx
@@ -2094,31 +2094,31 @@
         </is>
       </c>
       <c r="C40" s="3" t="n">
-        <v>0</v>
+        <v>1.226</v>
       </c>
       <c r="D40" s="3" t="n">
-        <v>0</v>
+        <v>3.476</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0</v>
+        <v>1.946</v>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0</v>
+        <v>2.094</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0</v>
+        <v>0.968</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0</v>
+        <v>0.732</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0</v>
+        <v>0.8080000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -2133,31 +2133,31 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>14.038</v>
+        <v>15.264</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>25.846</v>
+        <v>29.322</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>17.509</v>
+        <v>19.455</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>11.858</v>
+        <v>13.458</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>11.511</v>
+        <v>13.251</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>10.999</v>
+        <v>13.093</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>10.608</v>
+        <v>11.576</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>7.454</v>
+        <v>8.186</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>7.862</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="42">
@@ -2406,16 +2406,16 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.071</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.617</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.674</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.109</v>
+        <v>0.509</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>2.136</v>
@@ -3060,13 +3060,13 @@
         <v>0</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0</v>
+        <v>9.316000000000001</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>11.591</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>14.107</v>
       </c>
       <c r="J64" s="3" t="n">
         <v>0</v>
@@ -4765,10 +4765,10 @@
         <v>0</v>
       </c>
       <c r="H108" s="3" t="n">
-        <v>0</v>
+        <v>3.051</v>
       </c>
       <c r="I108" s="3" t="n">
-        <v>0</v>
+        <v>3.893</v>
       </c>
       <c r="J108" s="3" t="n">
         <v>0</v>
@@ -5269,19 +5269,19 @@
         <v>0</v>
       </c>
       <c r="G121" s="3" t="n">
-        <v>0</v>
+        <v>-0.047</v>
       </c>
       <c r="H121" s="3" t="n">
-        <v>0</v>
+        <v>-0.998</v>
       </c>
       <c r="I121" s="3" t="n">
-        <v>0</v>
+        <v>-1.552</v>
       </c>
       <c r="J121" s="3" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
       <c r="K121" s="3" t="n">
-        <v>0</v>
+        <v>-1.799</v>
       </c>
     </row>
     <row r="122">
@@ -12690,7 +12690,11 @@
           <t>Shares repurchased 9</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -13650,7 +13654,11 @@
           <t>Impairment charges 7</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -14238,7 +14246,11 @@
           <t>Shares repurchased 10</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -15182,7 +15194,11 @@
           <t>Shares repurchased 11</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -15562,7 +15578,11 @@
           <t>Impairment charge 7</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>AssetImpairmentCharge</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -20354,7 +20374,11 @@
           <t>Income tax recovery 13</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
